--- a/d/2026-08-06_会员有效性分析.xlsx
+++ b/d/2026-08-06_会员有效性分析.xlsx
@@ -14,6 +14,7 @@
     <sheet name="异常会员号码(跨门店高频)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="异常明细(订单级)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="内部业务礼品单" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="福建精准FX(剔除)" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,19 +556,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>566</v>
+        <v>546</v>
       </c>
       <c r="C6" t="n">
         <v>508</v>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>89.75</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>10.25</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="7">
@@ -1621,25 +1622,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>华为厦门思明罗宾森广场</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E38" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F38" t="n">
         <v>7</v>
       </c>
       <c r="G38" t="n">
-        <v>18.42</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="39">
@@ -1648,25 +1649,25 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>华为福州大洋晶典</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E39" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F39" t="n">
         <v>7</v>
       </c>
       <c r="G39" t="n">
-        <v>17.5</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="40">
@@ -1675,25 +1676,25 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>华为福州大洋晶典</t>
+          <t>DJI北京顺义华联授权体验店</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="E40" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F40" t="n">
         <v>7</v>
       </c>
       <c r="G40" t="n">
-        <v>23.33</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="41">
@@ -1702,25 +1703,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DJI北京顺义华联授权体验店</t>
+          <t>APR成都西宸天街</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E41" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>10.94</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="42">
@@ -1729,25 +1730,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>APR成都西宸天街</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E42" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F42" t="n">
         <v>6</v>
       </c>
       <c r="G42" t="n">
-        <v>10.34</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1756,25 +1757,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>APR成都温江伊藤</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="E43" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="F43" t="n">
         <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>8.960000000000001</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44">
@@ -1783,25 +1784,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>APR成都温江伊藤</t>
+          <t>DJI北京朝阳大悦城授权体验店</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="E44" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F44" t="n">
         <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>24</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="45">
@@ -1810,25 +1811,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DJI北京朝阳大悦城授权体验店</t>
+          <t>（旧）APR成都东安天街</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="F45" t="n">
         <v>6</v>
       </c>
       <c r="G45" t="n">
-        <v>10.34</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="46">
@@ -1837,25 +1838,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>（旧）APR成都东安天街</t>
+          <t>DJI北京丽泽天街授权体验店</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F46" t="n">
         <v>6</v>
       </c>
       <c r="G46" t="n">
-        <v>37.5</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="47">
@@ -1864,7 +1865,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DJI北京丽泽天街授权体验店</t>
+          <t>DJI北京龙湖熙悦天街授权体验店</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1873,16 +1874,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.09</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1891,7 +1892,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DJI北京龙湖熙悦天街授权体验店</t>
+          <t>DJI北京西北旺万象汇授权体验店</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1900,16 +1901,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F48" t="n">
         <v>5</v>
       </c>
       <c r="G48" t="n">
-        <v>8.619999999999999</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="49">
@@ -1918,25 +1919,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DJI北京西北旺万象汇授权体验店</t>
+          <t>DJI上海中庚漫游城授权体验店</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F49" t="n">
         <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>10.42</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -1945,25 +1946,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DJI上海中庚漫游城授权体验店</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F50" t="n">
         <v>5</v>
       </c>
       <c r="G50" t="n">
-        <v>8.619999999999999</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="51">
@@ -1972,25 +1973,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>DJI北京望京凯德MALL授权体验店</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E51" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F51" t="n">
         <v>5</v>
       </c>
       <c r="G51" t="n">
-        <v>8.93</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="52">
@@ -1999,25 +2000,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>华为厦门思明瑞景广场</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E52" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F52" t="n">
         <v>5</v>
       </c>
       <c r="G52" t="n">
-        <v>18.52</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="53">
@@ -2026,7 +2027,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>华为南平建阳建发悦城</t>
+          <t>华为南平武夷山宝龙广场</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2035,16 +2036,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E53" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F53" t="n">
         <v>5</v>
       </c>
       <c r="G53" t="n">
-        <v>18.52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54">
@@ -2053,25 +2054,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DJI北京望京凯德MALL授权体验店</t>
+          <t>DJI上海第一八佰伴授权体验店</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E54" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G54" t="n">
-        <v>11.63</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
@@ -2080,25 +2081,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>华为北京北苑龙湖</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E55" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G55" t="n">
-        <v>10.42</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="56">
@@ -2107,7 +2108,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>华为南平武夷山宝龙广场</t>
+          <t>华为福州东街口</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2116,16 +2117,16 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E56" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="57">
@@ -2134,25 +2135,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DJI上海第一八佰伴授权体验店</t>
+          <t>华为北京首开万象汇</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="E57" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="F57" t="n">
         <v>4</v>
       </c>
       <c r="G57" t="n">
-        <v>8</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="58">
@@ -2161,25 +2162,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>华为北京北苑龙湖</t>
+          <t>DJI上海静安大融城授权体验店</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E58" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F58" t="n">
         <v>4</v>
       </c>
       <c r="G58" t="n">
-        <v>9.76</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="59">
@@ -2188,25 +2189,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>华为福州东街口</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="E59" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="F59" t="n">
         <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>12.5</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="60">
@@ -2215,7 +2216,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>华为北京首开万象汇</t>
+          <t>华为北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2224,16 +2225,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E60" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>4.94</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="61">
@@ -2242,25 +2243,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DJI上海静安大融城授权体验店</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F61" t="n">
         <v>4</v>
       </c>
       <c r="G61" t="n">
-        <v>11.76</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="62">
@@ -2269,7 +2270,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>DJI北京龙湖亦庄天街授权体验店</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2278,16 +2279,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="E62" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F62" t="n">
         <v>4</v>
       </c>
       <c r="G62" t="n">
-        <v>5.56</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="63">
@@ -2296,7 +2297,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>华为北京亦庄龙湖</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2305,16 +2306,16 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E63" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="F63" t="n">
         <v>4</v>
       </c>
       <c r="G63" t="n">
-        <v>5.26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
@@ -2323,25 +2324,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>华为厦门湖里蔡塘爱琴海</t>
+          <t>DJI北京西红门荟聚中心授权体验店</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="E64" t="n">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G64" t="n">
-        <v>26.67</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="65">
@@ -2350,7 +2351,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>华为北京通州乐堤港</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2359,16 +2360,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E65" t="n">
+        <v>33</v>
+      </c>
+      <c r="F65" t="n">
         <v>3</v>
       </c>
-      <c r="F65" t="n">
-        <v>4</v>
-      </c>
       <c r="G65" t="n">
-        <v>57.14</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="66">
@@ -2377,25 +2378,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DJI北京龙湖亦庄天街授权体验店</t>
+          <t>APR北京顺义华联</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="E66" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
-        <v>7.69</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="67">
@@ -2404,25 +2405,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>DJI北京翠微百货授权体验店</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E67" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G67" t="n">
-        <v>16</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="68">
@@ -2431,25 +2432,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DJI北京西红门荟聚中心授权体验店</t>
+          <t>APR北京大峡谷凯德茂</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="E68" t="n">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="F68" t="n">
         <v>3</v>
       </c>
       <c r="G68" t="n">
-        <v>2.13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
@@ -2458,25 +2459,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>华为北京通州乐堤港</t>
+          <t>DJI北京通州万达授权体验店</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E69" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="F69" t="n">
         <v>3</v>
       </c>
       <c r="G69" t="n">
-        <v>8.33</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="70">
@@ -2485,25 +2486,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>APR北京顺义华联</t>
+          <t>DJI上海长风大悦城授权体验店</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="E70" t="n">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="F70" t="n">
         <v>3</v>
       </c>
       <c r="G70" t="n">
-        <v>3.37</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="71">
@@ -2512,25 +2513,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DJI北京翠微百货授权体验店</t>
+          <t>华为福州仓山爱琴海合作店</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="E71" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F71" t="n">
         <v>3</v>
       </c>
       <c r="G71" t="n">
-        <v>8.33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
@@ -2539,7 +2540,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>APR北京大峡谷凯德茂</t>
+          <t>APR北京西铁营万达</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2548,16 +2549,16 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E72" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F72" t="n">
         <v>3</v>
       </c>
       <c r="G72" t="n">
-        <v>12</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="73">
@@ -2566,25 +2567,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DJI北京通州万达授权体验店</t>
+          <t>APR成都双楠伊藤</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="E73" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="F73" t="n">
         <v>3</v>
       </c>
       <c r="G73" t="n">
-        <v>4.69</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="74">
@@ -2593,25 +2594,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DJI上海长风大悦城授权体验店</t>
+          <t>DJI北京龙湖大兴天街授权体验店</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E74" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F74" t="n">
         <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>15.79</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="75">
@@ -2620,7 +2621,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>华为福州仓山爱琴海合作店</t>
+          <t>华为厦门思明君尚天虹</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2629,16 +2630,16 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E75" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F75" t="n">
         <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="76">
@@ -2647,7 +2648,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>APR北京西铁营万达</t>
+          <t>APR北京新奥天虹</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2656,16 +2657,16 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E76" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F76" t="n">
         <v>3</v>
       </c>
       <c r="G76" t="n">
-        <v>11.11</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="77">
@@ -2674,25 +2675,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>华为福州砂之船奥莱</t>
+          <t>DJI北京丰科万达广场授权体验店</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="E77" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F77" t="n">
         <v>3</v>
       </c>
       <c r="G77" t="n">
-        <v>16.67</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="78">
@@ -2701,25 +2702,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>APR成都双楠伊藤</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E78" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F78" t="n">
         <v>3</v>
       </c>
       <c r="G78" t="n">
-        <v>13.64</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="79">
@@ -2728,25 +2729,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DJI北京龙湖大兴天街授权体验店</t>
+          <t>（旧）APR成都天府环宇坊</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="E79" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F79" t="n">
         <v>3</v>
       </c>
       <c r="G79" t="n">
-        <v>7.69</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="80">
@@ -2755,25 +2756,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>华为厦门思明君尚天虹</t>
+          <t>DJI上海漕河泾印象城授权体验店</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F80" t="n">
         <v>3</v>
       </c>
       <c r="G80" t="n">
-        <v>27.27</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="81">
@@ -2782,25 +2783,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>APR北京新奥天虹</t>
+          <t>DJI北京颐堤港授权体验店</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E81" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G81" t="n">
-        <v>16.67</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="82">
@@ -2809,25 +2810,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DJI北京丰科万达广场授权体验店</t>
+          <t>APR成都三利爱琴海</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D82" t="n">
         <v>48</v>
       </c>
       <c r="E82" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G82" t="n">
-        <v>6.25</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="83">
@@ -2836,25 +2837,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>华为福州中骏世界城</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="E83" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>7.5</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="84">
@@ -2863,25 +2864,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>（旧）APR成都天府环宇坊</t>
+          <t>华为厦门思明罗宾森广场</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G84" t="n">
-        <v>13.64</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="85">
@@ -2890,25 +2891,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DJI上海漕河泾印象城授权体验店</t>
+          <t>华为厦门思明宝龙一城</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E85" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G85" t="n">
-        <v>12.5</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="86">
@@ -2917,25 +2918,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DJI北京颐堤港授权体验店</t>
+          <t>华为北京东坝万达</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="E86" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="F86" t="n">
         <v>2</v>
       </c>
       <c r="G86" t="n">
-        <v>3.57</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="87">
@@ -2944,25 +2945,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>APR成都三利爱琴海</t>
+          <t>华为厦门思明加州广场</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="E87" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F87" t="n">
         <v>2</v>
       </c>
       <c r="G87" t="n">
-        <v>4.17</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="88">
@@ -2971,25 +2972,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>华为福州中骏世界城</t>
+          <t>华为北京门头沟长安天街</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E88" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F88" t="n">
         <v>2</v>
       </c>
       <c r="G88" t="n">
-        <v>2.74</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="89">
@@ -2998,25 +2999,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>华为厦门思明宝龙一城</t>
+          <t>APR北京五道口购物中心</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="E89" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="F89" t="n">
         <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>4.17</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="90">
@@ -3025,25 +3026,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>华为北京东坝万达</t>
+          <t>华为福州五四北泰禾广场</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="E90" t="n">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="F90" t="n">
         <v>2</v>
       </c>
       <c r="G90" t="n">
-        <v>1.98</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="91">
@@ -3052,25 +3053,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>华为厦门思明加州广场</t>
+          <t>APR成都天府大悦城</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D91" t="n">
+        <v>28</v>
+      </c>
+      <c r="E91" t="n">
         <v>26</v>
-      </c>
-      <c r="E91" t="n">
-        <v>24</v>
       </c>
       <c r="F91" t="n">
         <v>2</v>
       </c>
       <c r="G91" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="92">
@@ -3079,7 +3080,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>华为北京门头沟长安天街</t>
+          <t>华为北京沙河万达</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3088,16 +3089,16 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="E92" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F92" t="n">
         <v>2</v>
       </c>
       <c r="G92" t="n">
-        <v>3.77</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="93">
@@ -3106,25 +3107,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>APR北京五道口购物中心</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E93" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
         <v>2</v>
       </c>
       <c r="G93" t="n">
-        <v>6.9</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="94">
@@ -3133,25 +3134,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>华为福州五四北泰禾广场</t>
+          <t>华为北京丰台鑫嘉汇</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="E94" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="F94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>3.03</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="95">
@@ -3160,25 +3161,25 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>APR成都天府大悦城</t>
+          <t>华为泉州石狮泰禾广场</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E95" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>7.14</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="96">
@@ -3187,25 +3188,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>华为北京沙河万达</t>
+          <t>APR北京合生汇</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="E96" t="n">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>6.06</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="97">
@@ -3214,25 +3215,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E97" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="F97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>14.29</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="98">
@@ -3241,7 +3242,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>华为北京丰台鑫嘉汇</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3250,16 +3251,16 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E98" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="F98" t="n">
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>6.25</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="99">
@@ -3268,25 +3269,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>华为泉州石狮泰禾广场</t>
+          <t>APR北京大兴龙湖</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="E99" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F99" t="n">
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>1.79</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="100">
@@ -3295,25 +3296,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>APR北京合生汇</t>
+          <t>华为厦门思明瑞景广场</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="E100" t="n">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="F100" t="n">
         <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>0.78</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="101">
@@ -3322,7 +3323,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DJI上海世博天地授权体验店</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3331,16 +3332,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E101" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F101" t="n">
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>3.33</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="102">
@@ -3349,7 +3350,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3358,16 +3359,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E102" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F102" t="n">
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>2.22</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="103">
@@ -3376,25 +3377,25 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>APR北京大兴龙湖</t>
+          <t>APR成都蜀新天街</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E103" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="F103" t="n">
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>3.12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -3403,7 +3404,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>DJI上海百联南桥购物中心授权体验店</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3412,16 +3413,16 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E104" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F104" t="n">
         <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="105">
@@ -3430,25 +3431,25 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>APR北京万柳华联</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E105" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>3.7</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="106">
@@ -3457,25 +3458,25 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>APR成都蜀新天街</t>
+          <t>DJI上海维璟印象城授权体验店</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E106" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F106" t="n">
         <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="107">
@@ -3484,25 +3485,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DJI上海百联南桥购物中心授权体验店</t>
+          <t>华为福州平潭吾悦</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E107" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
       </c>
       <c r="G107" t="n">
-        <v>3.85</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="108">
@@ -3511,7 +3512,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>APR北京万柳华联</t>
+          <t>APR北京东坝万达</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3520,16 +3521,16 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E108" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F108" t="n">
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>5.56</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="109">
@@ -3538,25 +3539,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DJI上海维璟印象城授权体验店</t>
+          <t>APR北京五棵松华熙</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="E109" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
       </c>
       <c r="G109" t="n">
-        <v>2.33</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="110">
@@ -3565,25 +3566,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>华为福州平潭吾悦</t>
+          <t>华为北京回龙观万科</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E110" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F110" t="n">
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>3.23</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="111">
@@ -3592,25 +3593,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>APR北京东坝万达</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E111" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="112">
@@ -3619,25 +3620,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>APR北京五棵松华熙</t>
+          <t>华为北京丽泽龙湖</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="E112" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>1.3</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="113">
@@ -3646,25 +3647,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>华为北京回龙观万科</t>
+          <t>华为福州宜家荟聚</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E113" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>7.14</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="114">
@@ -3673,25 +3674,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>华为厦门思明大西洋天虹</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E114" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>2.86</v>
+        <v>25</v>
       </c>
     </row>
     <row r="115">
@@ -3700,25 +3701,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>华为北京丽泽龙湖</t>
+          <t>APR成都龙泉吾悦</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E115" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="F115" t="n">
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>1.89</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="116">
@@ -3727,7 +3728,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>华为福州宜家荟聚</t>
+          <t>华为厦门湖里蔡塘爱琴海</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3736,16 +3737,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E116" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>11.11</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="117">
@@ -3754,25 +3755,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>华为厦门思明大西洋天虹</t>
+          <t>APR北京大红门银泰</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E117" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F117" t="n">
         <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>25</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="118">
@@ -3781,7 +3782,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>APR成都龙泉吾悦</t>
+          <t>APR成都北城天街</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3790,16 +3791,16 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E118" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>6.25</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="119">
@@ -3808,25 +3809,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>APR北京大红门银泰</t>
+          <t>DJI北京昌平超级合生汇授权体验店</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E119" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -3835,25 +3836,25 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>APR成都北城天街</t>
+          <t>DJI上海江桥万达授权体验店</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E120" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3862,19 +3863,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DJI北京昌平超级合生汇授权体验店</t>
+          <t>华为北京石景山万达</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="E121" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -3889,19 +3890,19 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DJI上海江桥万达授权体验店</t>
+          <t>APR北京丽泽龙湖</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E122" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F122" t="n">
         <v>0</v>
@@ -3916,19 +3917,19 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>华为北京石景山万达</t>
+          <t>APR北京望京华彩</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="E123" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
@@ -3943,7 +3944,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>APR北京丽泽龙湖</t>
+          <t>APR北京通州万达</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3952,10 +3953,10 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E124" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -3970,19 +3971,19 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>APR北京望京华彩</t>
+          <t>DJI上海FFC滨江悅里授权体验店</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E125" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -3997,19 +3998,19 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>APR北京通州万达</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E126" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -4024,19 +4025,19 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DJI上海FFC滨江悅里授权体验店</t>
+          <t>APR北京石景山万达</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="E127" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -4051,19 +4052,19 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>APR北京亦庄龙湖</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E128" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -4078,7 +4079,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>APR北京石景山万达</t>
+          <t>APR北京常营龙湖</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4087,10 +4088,10 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E129" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -4105,19 +4106,19 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>APR北京亦庄龙湖</t>
+          <t>华为北京牡丹园翠微</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="E130" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -4132,19 +4133,19 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>APR北京常营龙湖</t>
+          <t>DJI北京东坝万达广场授权体验店</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="E131" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -4159,7 +4160,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>华为北京牡丹园翠微</t>
+          <t>华为北京酒仙桥颐堤港</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4168,10 +4169,10 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E132" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -4186,19 +4187,19 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DJI北京东坝万达广场授权体验店</t>
+          <t>华为北京大兴大族</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E133" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -4213,19 +4214,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>华为北京酒仙桥颐堤港</t>
+          <t>APR北京同成街华联</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="E134" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F134" t="n">
         <v>0</v>
@@ -4240,19 +4241,19 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>华为北京大兴大族</t>
+          <t>APR北京槐房万达</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E135" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F135" t="n">
         <v>0</v>
@@ -4267,19 +4268,19 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>APR北京同成街华联</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E136" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F136" t="n">
         <v>0</v>
@@ -4294,7 +4295,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>APR北京槐房万达</t>
+          <t>APR北京大族广场</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4303,10 +4304,10 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E137" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -4321,19 +4322,19 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>华为北京回龙观一店</t>
+          <t>DJI北京龙德广场授权体验店</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="E138" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -4348,19 +4349,19 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>APR北京大族广场</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E139" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -4375,19 +4376,19 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DJI北京龙德广场授权体验店</t>
+          <t>华为北京丰科万达</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="E140" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="F140" t="n">
         <v>0</v>
@@ -4402,7 +4403,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>华为北京平谷万达</t>
+          <t>华为北京长楹龙湖</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4411,10 +4412,10 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="E141" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -4429,19 +4430,19 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>华为北京丰科万达</t>
+          <t>APR北京石景山喜隆多</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="E142" t="n">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -4456,19 +4457,19 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>华为北京长楹龙湖</t>
+          <t>华为南平建阳建发悦城</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="E143" t="n">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -4483,19 +4484,19 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>APR北京石景山喜隆多</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="E144" t="n">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -4510,19 +4511,19 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>APR北京龙德广场</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="E145" t="n">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -4537,7 +4538,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>APR北京龙德广场</t>
+          <t>APR北京海淀大悦城</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4546,10 +4547,10 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="E146" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -4564,7 +4565,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>APR北京海淀大悦城</t>
+          <t>APR北京望京凯德茂</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4573,10 +4574,10 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E147" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -4591,7 +4592,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>APR北京望京凯德茂</t>
+          <t>APR北京回龙观华联</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4600,10 +4601,10 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E148" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -4618,7 +4619,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>APR北京回龙观华联</t>
+          <t>APR北京房山熙悦</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4627,10 +4628,10 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E149" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -4645,19 +4646,19 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>APR北京房山熙悦</t>
+          <t>华为福州砂之船奥莱</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="E150" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -5335,14 +5336,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
       <c r="C2" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>各分公司门店数：上海爱飞 16家、北京中恒 7家、北京易联 17家、北京飞航 33家、四川新跃 19家、福建易联 18家</t>
+          <t>各分公司门店数：上海爱飞 16家、北京中恒 7家、北京易联 17家、北京飞航 33家、四川新跃 19家、福建易联 16家</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5354,7 +5355,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>137****7690</t>
+          <t>135****5980</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5365,7 +5366,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DJI北京万柳华联授权体验店</t>
+          <t>DJI北京蓝色港湾授权体验店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5377,7 +5378,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>131****7183</t>
+          <t>137****7690</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5388,19 +5389,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>华为北京怀柔万达</t>
+          <t>DJI北京万柳华联授权体验店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>135****5980</t>
+          <t>131****7183</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5411,12 +5412,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DJI北京蓝色港湾授权体验店</t>
+          <t>华为北京怀柔万达</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5447,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>159****4633</t>
+          <t>139****6069</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5457,19 +5458,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>APR成都科华王府井</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>131****2308</t>
+          <t>130****8344</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5480,19 +5481,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>130****8344</t>
+          <t>131****2308</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5503,19 +5504,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>177****6608</t>
+          <t>159****4633</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5526,12 +5527,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>APR成都科华王府井</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5562,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>135****5842</t>
+          <t>186****1441</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5572,19 +5573,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>DJI大疆哈苏北京芳草地概念店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>139****6069</t>
+          <t>135****5842</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -5595,7 +5596,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5607,7 +5608,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>186****1441</t>
+          <t>177****6608</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5618,19 +5619,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京芳草地概念店</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>182****4467</t>
+          <t>136****4463</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5641,7 +5642,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>华为北京亦庄龙湖</t>
+          <t>华为北京延庆万达</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5653,7 +5654,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>136****3123</t>
+          <t>182****4467</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5664,19 +5665,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DJI北京中关村大融城授权体验店</t>
+          <t>华为北京亦庄龙湖</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>139****3525</t>
+          <t>152****9221</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5687,19 +5688,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>APR成都西宸天街</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>138****6407</t>
+          <t>135****7736</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -5710,19 +5711,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DJI上海中庚漫游城授权体验店</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>139****1328</t>
+          <t>158****3312</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5733,19 +5734,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>华为北京首开万象汇</t>
+          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>135****5632</t>
+          <t>156****7796</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -5756,19 +5757,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DJI北京万柳华联授权体验店</t>
+          <t>APR北京新奥天虹</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>158****7802</t>
+          <t>139****3924</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5779,7 +5780,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>华为北京同成街华联</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5791,7 +5792,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>195****9249</t>
+          <t>181****8520</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5802,19 +5803,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DJI上海长宁龙之梦授权体验店</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>139****0982</t>
+          <t>136****3123</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5825,7 +5826,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
+          <t>DJI北京中关村大融城授权体验店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5837,7 +5838,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>156****7796</t>
+          <t>172****0421</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -5848,19 +5849,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>APR北京新奥天虹</t>
+          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>185****1969</t>
+          <t>135****5632</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -5871,12 +5872,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>DJI北京万柳华联授权体验店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5907,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>138****3402</t>
+          <t>136****0388</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -5917,19 +5918,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DJI上海美罗城授权体验店</t>
+          <t>DJI大疆哈苏北京大兴机场概念店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>185****1655</t>
+          <t>185****1969</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -5940,7 +5941,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>华为北京北苑龙湖</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5975,7 +5976,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>186****9390</t>
+          <t>195****9249</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -5986,19 +5987,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>DJI上海长宁龙之梦授权体验店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>172****0421</t>
+          <t>138****6407</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -6009,19 +6010,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
+          <t>DJI上海中庚漫游城授权体验店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>150****3076</t>
+          <t>186****8905</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -6032,19 +6033,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>华为北京通州乐堤港</t>
+          <t>DJI北京西北旺万象汇授权体验店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>136****0388</t>
+          <t>136****3198</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -6055,19 +6056,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京大兴机场概念店</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>158****3312</t>
+          <t>138****0277</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -6078,7 +6079,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京华熙LIVE概念店</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6090,7 +6091,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>139****3924</t>
+          <t>188****7964</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -6101,19 +6102,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>APR北京大峡谷凯德茂</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>135****5494</t>
+          <t>138****3402</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -6124,7 +6125,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>DJI上海美罗城授权体验店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6136,7 +6137,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>135****7736</t>
+          <t>136****4467</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -6147,19 +6148,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>华为北京来福士</t>
+          <t>APR北京西铁营万达</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>177****0077</t>
+          <t>139****1328</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -6170,7 +6171,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>华为北京来福士</t>
+          <t>华为北京首开万象汇</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6182,7 +6183,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>181****8520</t>
+          <t>150****3076</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -6193,19 +6194,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>华为北京通州乐堤港</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>136****4467</t>
+          <t>139****3525</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -6216,19 +6217,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>APR北京西铁营万达</t>
+          <t>APR成都西宸天街</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>152****9221</t>
+          <t>136****5338</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -6239,19 +6240,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>DJI北京朝阳大悦城授权体验店</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>135****0175</t>
+          <t>182****0958</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -6262,19 +6263,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>APR北京顺义华联</t>
+          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>138****0277</t>
+          <t>135****0175</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -6285,19 +6286,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>APR北京顺义华联</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>136****3198</t>
+          <t>139****0982</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -6308,19 +6309,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>华为北京来福士</t>
+          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>136****4463</t>
+          <t>158****7802</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -6331,7 +6332,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>华为北京延庆万达</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6343,7 +6344,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>186****8905</t>
+          <t>186****9390</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -6354,7 +6355,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DJI北京西北旺万象汇授权体验店</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6366,7 +6367,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>182****0958</t>
+          <t>135****5494</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -6377,19 +6378,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京朝阳合生汇概念店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>136****5338</t>
+          <t>177****0077</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -6400,19 +6401,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DJI北京朝阳大悦城授权体验店</t>
+          <t>华为北京来福士</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>188****7964</t>
+          <t>185****1655</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -6423,12 +6424,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>APR北京大峡谷凯德茂</t>
+          <t>华为北京北苑龙湖</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6501,7 +6502,7 @@
         <v>39</v>
       </c>
       <c r="F2" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="3">
@@ -6527,7 +6528,7 @@
         <v>39</v>
       </c>
       <c r="F3" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="4">
@@ -6553,7 +6554,7 @@
         <v>38</v>
       </c>
       <c r="F4" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="5">
@@ -6579,7 +6580,7 @@
         <v>33</v>
       </c>
       <c r="F5" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="6">
@@ -6631,7 +6632,7 @@
         <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8">
@@ -6709,7 +6710,7 @@
         <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="11">
@@ -6813,7 +6814,7 @@
         <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="15">
@@ -6865,7 +6866,7 @@
         <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="17">
@@ -6891,7 +6892,7 @@
         <v>21</v>
       </c>
       <c r="F17" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="18">
@@ -6943,7 +6944,7 @@
         <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="20">
@@ -6995,7 +6996,7 @@
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="22">
@@ -7021,7 +7022,7 @@
         <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="23">
@@ -7047,7 +7048,7 @@
         <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="24">
@@ -7099,7 +7100,7 @@
         <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="26">
@@ -7203,7 +7204,7 @@
         <v>19</v>
       </c>
       <c r="F29" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="30">
@@ -7229,7 +7230,7 @@
         <v>14</v>
       </c>
       <c r="F30" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="31">
@@ -7281,7 +7282,7 @@
         <v>14</v>
       </c>
       <c r="F32" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="33">
@@ -7307,7 +7308,7 @@
         <v>14</v>
       </c>
       <c r="F33" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="34">
@@ -7333,7 +7334,7 @@
         <v>14</v>
       </c>
       <c r="F34" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="35">
@@ -7359,7 +7360,7 @@
         <v>8</v>
       </c>
       <c r="F35" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="36">
@@ -7411,7 +7412,7 @@
         <v>13</v>
       </c>
       <c r="F37" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="38">
@@ -7437,7 +7438,7 @@
         <v>13</v>
       </c>
       <c r="F38" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="39">
@@ -7463,7 +7464,7 @@
         <v>12</v>
       </c>
       <c r="F39" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="40">
@@ -7489,7 +7490,7 @@
         <v>11</v>
       </c>
       <c r="F40" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="41">
@@ -7515,7 +7516,7 @@
         <v>11</v>
       </c>
       <c r="F41" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="42">
@@ -7593,7 +7594,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="45">
@@ -7619,7 +7620,7 @@
         <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="46">
@@ -7645,7 +7646,7 @@
         <v>6</v>
       </c>
       <c r="F46" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="47">
@@ -7697,7 +7698,7 @@
         <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="49">
@@ -7716,7 +7717,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>139****3924</t>
+          <t>185****1969</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -7742,7 +7743,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>185****1969</t>
+          <t>139****3924</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -7775,7 +7776,7 @@
         <v>7</v>
       </c>
       <c r="F51" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="52">
@@ -7827,7 +7828,7 @@
         <v>10</v>
       </c>
       <c r="F53" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="54">
@@ -7853,7 +7854,7 @@
         <v>9</v>
       </c>
       <c r="F54" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="55">
@@ -7931,7 +7932,7 @@
         <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="58">
@@ -8035,7 +8036,7 @@
         <v>7</v>
       </c>
       <c r="F61" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="62">
@@ -8093,12 +8094,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>华为厦门思明罗宾森广场</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -8110,10 +8111,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="65">
@@ -8132,25 +8133,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>135****5494</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
-        <v>730</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>华为福州大洋晶典</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -8158,25 +8159,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>135****5494</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>华为福州大洋晶典</t>
+          <t>DJI北京顺义华联授权体验店</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -8191,22 +8192,22 @@
         <v>7</v>
       </c>
       <c r="F67" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DJI北京顺义华联授权体验店</t>
+          <t>APR成都西宸天街</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8214,10 +8215,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F68" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="69">
@@ -8249,12 +8250,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>APR成都西宸天街</t>
+          <t>DJI北京昌平悦荟授权体验店</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -8269,7 +8270,7 @@
         <v>3</v>
       </c>
       <c r="F70" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="71">
@@ -8288,25 +8289,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>138****0277</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>3</v>
       </c>
       <c r="F71" t="n">
-        <v>730</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DJI北京昌平悦荟授权体验店</t>
+          <t>APR成都温江伊藤</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -8314,25 +8315,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>138****0277</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>APR成都温江伊藤</t>
+          <t>DJI北京朝阳大悦城授权体验店</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -8344,10 +8345,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="74">
@@ -8366,25 +8367,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>136****5338</t>
         </is>
       </c>
       <c r="E74" t="n">
         <v>3</v>
       </c>
       <c r="F74" t="n">
-        <v>730</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DJI北京朝阳大悦城授权体验店</t>
+          <t>（旧）APR成都东安天街</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -8392,25 +8393,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>136****5338</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>（旧）APR成都东安天街</t>
+          <t>DJI北京丽泽天街授权体验店</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -8425,13 +8426,13 @@
         <v>6</v>
       </c>
       <c r="F76" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DJI北京丽泽天街授权体验店</t>
+          <t>DJI北京龙湖熙悦天街授权体验店</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8440,7 +8441,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8448,16 +8449,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DJI北京龙湖熙悦天街授权体验店</t>
+          <t>DJI北京西北旺万象汇授权体验店</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8470,14 +8471,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>186****8905</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F78" t="n">
-        <v>730</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -8496,25 +8497,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>186****8905</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DJI北京西北旺万象汇授权体验店</t>
+          <t>DJI上海中庚漫游城授权体验店</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -8522,14 +8523,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>138****6407</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80" t="n">
-        <v>730</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -8548,25 +8549,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>138****6407</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DJI上海中庚漫游城授权体验店</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -8574,14 +8575,14 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>152****9221</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="n">
-        <v>730</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -8600,25 +8601,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>152****9221</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>DJI北京望京凯德MALL授权体验店</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -8630,21 +8631,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F84" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>华为厦门思明瑞景广场</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -8652,25 +8653,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>181****8520</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>730</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>华为南平建阳建发悦城</t>
+          <t>APR成都武侯大悦城</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -8682,21 +8683,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DJI北京望京凯德MALL授权体验店</t>
+          <t>华为南平武夷山宝龙广场</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -8711,74 +8712,74 @@
         <v>5</v>
       </c>
       <c r="F87" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>DJI上海第一八佰伴授权体验店</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>181****8520</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>APR成都武侯大悦城</t>
+          <t>华为北京北苑龙湖</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>185****1655</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F89" t="n">
-        <v>730</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>华为南平武夷山宝龙广场</t>
+          <t>华为北京北苑龙湖</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8786,21 +8787,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DJI上海第一八佰伴授权体验店</t>
+          <t>华为福州东街口</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -8815,13 +8816,13 @@
         <v>4</v>
       </c>
       <c r="F91" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>华为北京北苑龙湖</t>
+          <t>华为北京首开万象汇</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8834,7 +8835,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>185****1655</t>
+          <t>139****1328</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -8847,7 +8848,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>华为北京北苑龙湖</t>
+          <t>华为北京首开万象汇</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8867,18 +8868,18 @@
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>华为福州东街口</t>
+          <t>DJI上海静安大融城授权体验店</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -8893,18 +8894,18 @@
         <v>4</v>
       </c>
       <c r="F94" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>华为北京首开万象汇</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -8912,7 +8913,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>139****1328</t>
+          <t>186****9390</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -8925,12 +8926,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>华为北京首开万象汇</t>
+          <t>DJI北京京西大悦城授权体验店</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -8945,18 +8946,18 @@
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DJI上海静安大融城授权体验店</t>
+          <t>华为北京亦庄龙湖</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -8964,25 +8965,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>182****4467</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F97" t="n">
-        <v>730</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>华为北京亦庄龙湖</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -8990,25 +8991,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>186****9390</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DJI北京京西大悦城授权体验店</t>
+          <t>华为北京京投小站</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -9016,25 +9017,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>131****2308</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F99" t="n">
-        <v>730</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>华为北京亦庄龙湖</t>
+          <t>DJI北京龙湖亦庄天街授权体验店</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -9042,20 +9043,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>182****4467</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>华为北京亦庄龙湖</t>
+          <t>华为北京汇琴广场</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9068,29 +9069,29 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>139****6069</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F101" t="n">
-        <v>730</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>华为厦门湖里蔡塘爱琴海</t>
+          <t>DJI北京西红门荟聚中心授权体验店</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9098,16 +9099,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F102" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>华为北京京投小站</t>
+          <t>华为北京通州乐堤港</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9116,81 +9117,81 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>131****2308</t>
+          <t>150****3076</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DJI北京龙湖亦庄天街授权体验店</t>
+          <t>APR北京顺义华联</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>135****0175</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F104" t="n">
-        <v>730</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>华为北京汇琴广场</t>
+          <t>DJI北京翠微百货授权体验店</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>139****6069</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F105" t="n">
-        <v>4</v>
+        <v>710</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DJI北京西红门荟聚中心授权体验店</t>
+          <t>APR北京大峡谷凯德茂</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -9198,25 +9199,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>188****7964</t>
         </is>
       </c>
       <c r="E106" t="n">
         <v>3</v>
       </c>
       <c r="F106" t="n">
-        <v>730</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>华为北京通州乐堤港</t>
+          <t>DJI北京通州万达授权体验店</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -9224,25 +9225,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>150****3076</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E107" t="n">
         <v>3</v>
       </c>
       <c r="F107" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>APR北京顺义华联</t>
+          <t>DJI上海长风大悦城授权体验店</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -9250,25 +9251,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>135****0175</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E108" t="n">
         <v>3</v>
       </c>
       <c r="F108" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DJI北京翠微百货授权体验店</t>
+          <t>华为福州仓山爱琴海合作店</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -9283,13 +9284,13 @@
         <v>3</v>
       </c>
       <c r="F109" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>APR北京大峡谷凯德茂</t>
+          <t>APR北京西铁营万达</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9302,7 +9303,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>188****7964</t>
+          <t>136****4467</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -9315,12 +9316,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DJI北京通州万达授权体验店</t>
+          <t>APR成都双楠伊藤</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -9335,18 +9336,18 @@
         <v>3</v>
       </c>
       <c r="F111" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DJI上海长风大悦城授权体验店</t>
+          <t>DJI北京龙湖大兴天街授权体验店</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -9361,13 +9362,13 @@
         <v>3</v>
       </c>
       <c r="F112" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>华为福州仓山爱琴海合作店</t>
+          <t>华为厦门思明君尚天虹</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9387,13 +9388,13 @@
         <v>3</v>
       </c>
       <c r="F113" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>APR北京西铁营万达</t>
+          <t>APR北京新奥天虹</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9406,7 +9407,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>136****4467</t>
+          <t>156****7796</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -9419,12 +9420,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>华为福州砂之船奥莱</t>
+          <t>DJI北京丰科万达广场授权体验店</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -9439,18 +9440,18 @@
         <v>3</v>
       </c>
       <c r="F115" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>APR成都双楠伊藤</t>
+          <t>华为北京房山万科</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -9465,18 +9466,18 @@
         <v>3</v>
       </c>
       <c r="F116" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DJI北京龙湖大兴天街授权体验店</t>
+          <t>（旧）APR成都天府环宇坊</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -9491,18 +9492,18 @@
         <v>3</v>
       </c>
       <c r="F117" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>华为厦门思明君尚天虹</t>
+          <t>DJI上海漕河泾印象城授权体验店</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -9517,48 +9518,48 @@
         <v>3</v>
       </c>
       <c r="F118" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>APR北京新奥天虹</t>
+          <t>DJI北京颐堤港授权体验店</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>156****7796</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F119" t="n">
-        <v>3</v>
+        <v>710</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DJI北京丰科万达广场授权体验店</t>
+          <t>APR成都三利爱琴海</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9566,25 +9567,25 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F120" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>华为北京房山万科</t>
+          <t>华为福州中骏世界城</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9592,25 +9593,25 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F121" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>（旧）APR成都天府环宇坊</t>
+          <t>华为厦门思明罗宾森广场</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9618,25 +9619,25 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F122" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DJI上海漕河泾印象城授权体验店</t>
+          <t>华为厦门思明宝龙一城</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9644,21 +9645,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F123" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DJI北京颐堤港授权体验店</t>
+          <t>华为北京东坝万达</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -9673,18 +9674,18 @@
         <v>2</v>
       </c>
       <c r="F124" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>APR成都三利爱琴海</t>
+          <t>华为厦门思明加州广场</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -9699,18 +9700,18 @@
         <v>2</v>
       </c>
       <c r="F125" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>华为福州中骏世界城</t>
+          <t>华为北京门头沟长安天街</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -9725,18 +9726,18 @@
         <v>2</v>
       </c>
       <c r="F126" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>华为厦门思明宝龙一城</t>
+          <t>APR北京五道口购物中心</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -9751,18 +9752,18 @@
         <v>2</v>
       </c>
       <c r="F127" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>华为北京东坝万达</t>
+          <t>华为福州五四北泰禾广场</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -9777,18 +9778,18 @@
         <v>2</v>
       </c>
       <c r="F128" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>华为厦门思明加州广场</t>
+          <t>APR成都天府大悦城</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -9803,13 +9804,13 @@
         <v>2</v>
       </c>
       <c r="F129" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>华为北京门头沟长安天街</t>
+          <t>华为北京沙河万达</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9829,18 +9830,18 @@
         <v>2</v>
       </c>
       <c r="F130" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>APR北京五道口购物中心</t>
+          <t>华为北京昌平政府街</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -9855,22 +9856,22 @@
         <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>华为福州五四北泰禾广场</t>
+          <t>华为北京丰台鑫嘉汇</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9878,25 +9879,25 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F132" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>APR成都天府大悦城</t>
+          <t>华为泉州石狮泰禾广场</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9904,25 +9905,25 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>华为北京沙河万达</t>
+          <t>APR北京合生汇</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9930,25 +9931,25 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>华为北京昌平政府街</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9956,16 +9957,16 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F135" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>华为北京丰台鑫嘉汇</t>
+          <t>华为北京丰台银泰</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9985,18 +9986,18 @@
         <v>1</v>
       </c>
       <c r="F136" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>华为泉州石狮泰禾广场</t>
+          <t>APR北京大兴龙湖</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -10011,18 +10012,18 @@
         <v>1</v>
       </c>
       <c r="F137" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>APR北京合生汇</t>
+          <t>华为厦门思明瑞景广场</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -10037,13 +10038,13 @@
         <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DJI上海世博天地授权体验店</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10063,13 +10064,13 @@
         <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>华为北京丰台银泰</t>
+          <t>华为北京回龙观华联</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10089,18 +10090,18 @@
         <v>1</v>
       </c>
       <c r="F140" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>APR北京大兴龙湖</t>
+          <t>APR成都蜀新天街</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -10115,13 +10116,13 @@
         <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>DJI上海百联南桥购物中心授权体验店</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10141,18 +10142,18 @@
         <v>1</v>
       </c>
       <c r="F142" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>华为北京回龙观华联</t>
+          <t>APR北京万柳华联</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -10167,18 +10168,18 @@
         <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>APR成都蜀新天街</t>
+          <t>DJI上海维璟印象城授权体验店</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -10193,18 +10194,18 @@
         <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>DJI上海百联南桥购物中心授权体验店</t>
+          <t>华为福州平潭吾悦</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -10219,13 +10220,13 @@
         <v>1</v>
       </c>
       <c r="F145" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>APR北京万柳华联</t>
+          <t>APR北京东坝万达</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10245,18 +10246,18 @@
         <v>1</v>
       </c>
       <c r="F146" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DJI上海维璟印象城授权体验店</t>
+          <t>APR北京五棵松华熙</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -10271,18 +10272,18 @@
         <v>1</v>
       </c>
       <c r="F147" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>华为福州平潭吾悦</t>
+          <t>华为北京回龙观万科</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -10297,18 +10298,18 @@
         <v>1</v>
       </c>
       <c r="F148" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>APR北京东坝万达</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -10323,18 +10324,18 @@
         <v>1</v>
       </c>
       <c r="F149" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>APR北京五棵松华熙</t>
+          <t>华为北京丽泽龙湖</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -10349,18 +10350,18 @@
         <v>1</v>
       </c>
       <c r="F150" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>华为北京回龙观万科</t>
+          <t>华为福州宜家荟聚</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -10375,18 +10376,18 @@
         <v>1</v>
       </c>
       <c r="F151" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>华为厦门思明大西洋天虹</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -10401,18 +10402,18 @@
         <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>华为北京丽泽龙湖</t>
+          <t>APR成都龙泉吾悦</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -10427,13 +10428,13 @@
         <v>1</v>
       </c>
       <c r="F153" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>华为福州宜家荟聚</t>
+          <t>华为厦门湖里蔡塘爱琴海</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10453,18 +10454,18 @@
         <v>1</v>
       </c>
       <c r="F154" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>华为厦门思明大西洋天虹</t>
+          <t>APR北京大红门银泰</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>北京中恒</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -10479,13 +10480,13 @@
         <v>1</v>
       </c>
       <c r="F155" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>APR成都龙泉吾悦</t>
+          <t>APR成都北城天街</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10505,59 +10506,7 @@
         <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>APR北京大红门银泰</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>北京中恒</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>1</v>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>177****3777</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>1</v>
-      </c>
-      <c r="F157" t="n">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>APR成都北城天街</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>1</v>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>177****3777</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>1</v>
-      </c>
-      <c r="F158" t="n">
-        <v>730</v>
+        <v>710</v>
       </c>
     </row>
   </sheetData>
@@ -29711,4 +29660,690 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>订单日期</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>所属分公司</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>门店名称</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>订单号</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>会员手机号</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>销售员</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>华为福州砂之船奥莱</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LSD2026080100897888</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>刘树恒</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>华为福州砂之船奥莱</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LSD2026080300910100</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>刘树恒</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>华为福州砂之船奥莱</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LSD2026080500921122</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>刘树恒</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>华为南平建阳建发悦城</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LSD2026080100894898</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>简国庆</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>华为南平建阳建发悦城</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LSD2026080100895614</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>简国庆</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>华为南平建阳建发悦城</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LSD2026080600925244</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>简国庆</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>华为南平建阳建发悦城</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LSD2026080600925251</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>简国庆</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>华为南平建阳建发悦城</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LSD2026080600925273</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>简国庆</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>华为厦门思明瑞景广场</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LSD2026080300910848</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>华为厦门思明罗宾森广场</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LSD2026080400914796</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>华为厦门思明罗宾森广场</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LSD2026080400914859</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>华为厦门湖里蔡塘爱琴海</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LSD2026080400914556</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>华为厦门思明瑞景广场</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LSD2026080500921116</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>华为厦门思明瑞景广场</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LSD2026080500921137</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>华为厦门思明瑞景广场</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LSD2026080500921406</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>华为厦门思明罗宾森广场</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LSD2026080500920720</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>华为厦门思明罗宾森广场</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LSD2026080500921208</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>华为厦门思明罗宾森广场</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LSD2026080500922631</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>华为厦门湖里蔡塘爱琴海</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LSD2026080500920539</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>福建易联</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>华为厦门湖里蔡塘爱琴海</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LSD2026080500921399</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>177****3777</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>陈青松</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>